--- a/results/fptl_floyd.xlsx
+++ b/results/fptl_floyd.xlsx
@@ -470,28 +470,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0163</v>
+        <v>0.0174999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0179</v>
+        <v>0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0535</v>
+        <v>0.0548999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0545999999999999</v>
+        <v>0.0577999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2624000000000001</v>
+        <v>0.2707999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2871</v>
+        <v>0.2575999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>23.6973</v>
+        <v>22.7217</v>
       </c>
       <c r="I2" t="n">
-        <v>24.473</v>
+        <v>23.1714</v>
       </c>
     </row>
     <row r="3">
@@ -499,28 +499,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0208999999999999</v>
+        <v>0.0193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0225</v>
+        <v>0.0209</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0847999999999999</v>
+        <v>0.0760999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0870999999999999</v>
+        <v>0.0677</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3137999999999999</v>
+        <v>0.2858</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3258</v>
+        <v>0.2853</v>
       </c>
       <c r="H3" t="n">
-        <v>14.13</v>
+        <v>14.1078</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3509</v>
+        <v>14.552</v>
       </c>
     </row>
     <row r="4">
@@ -528,28 +528,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0215</v>
+        <v>0.0221999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0237</v>
+        <v>0.0227999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1028</v>
+        <v>0.08829999999999991</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1002</v>
+        <v>0.0841999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3441999999999999</v>
+        <v>0.2916999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3381</v>
+        <v>0.2994</v>
       </c>
       <c r="H4" t="n">
-        <v>11.2877</v>
+        <v>14.0513</v>
       </c>
       <c r="I4" t="n">
-        <v>11.628</v>
+        <v>13.9125</v>
       </c>
     </row>
     <row r="5">
@@ -557,28 +557,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0280999999999999</v>
+        <v>0.0262</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0241</v>
+        <v>0.0243</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1018999999999999</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1075</v>
+        <v>0.1011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3611</v>
+        <v>0.3078</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3727</v>
+        <v>0.3186999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>10.2654</v>
+        <v>9.938999999999998</v>
       </c>
       <c r="I5" t="n">
-        <v>10.7067</v>
+        <v>10.2767</v>
       </c>
     </row>
     <row r="6">
@@ -586,28 +586,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.028</v>
+        <v>0.0237</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0308</v>
+        <v>0.0267</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1123</v>
+        <v>0.113</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1166</v>
+        <v>0.1111</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3613999999999999</v>
+        <v>0.3424999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3821</v>
+        <v>0.363</v>
       </c>
       <c r="H6" t="n">
-        <v>10.559</v>
+        <v>10.8416</v>
       </c>
       <c r="I6" t="n">
-        <v>10.7763</v>
+        <v>11.2576</v>
       </c>
     </row>
     <row r="7">
@@ -615,28 +615,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0334999999999999</v>
+        <v>0.0306999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0315</v>
+        <v>0.0272</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1218999999999999</v>
+        <v>0.1234</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1251</v>
+        <v>0.1139999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3669999999999999</v>
+        <v>0.3601999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3727</v>
+        <v>0.3757999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>10.8019</v>
+        <v>10.6896</v>
       </c>
       <c r="I7" t="n">
-        <v>11.1819</v>
+        <v>11.0952</v>
       </c>
     </row>
     <row r="8">
@@ -647,25 +647,25 @@
         <v>0.0306</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0324</v>
+        <v>0.0291999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1226</v>
+        <v>0.1232</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1262</v>
+        <v>0.1185</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3775999999999999</v>
+        <v>0.3903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3899999999999999</v>
+        <v>0.3646</v>
       </c>
       <c r="H8" t="n">
-        <v>11.0435</v>
+        <v>10.7208</v>
       </c>
       <c r="I8" t="n">
-        <v>11.2504</v>
+        <v>10.9277</v>
       </c>
     </row>
     <row r="9">
@@ -673,28 +673,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0358</v>
+        <v>0.0269</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0315</v>
+        <v>0.0309</v>
       </c>
       <c r="D9" t="n">
-        <v>0.142</v>
+        <v>0.1331999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1376</v>
+        <v>0.1369999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4064</v>
+        <v>0.3803999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3955</v>
+        <v>0.3947</v>
       </c>
       <c r="H9" t="n">
-        <v>10.8711</v>
+        <v>10.4631</v>
       </c>
       <c r="I9" t="n">
-        <v>11.4206</v>
+        <v>10.7477</v>
       </c>
     </row>
     <row r="10">
@@ -702,28 +702,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0354</v>
+        <v>0.0319</v>
       </c>
       <c r="C10" t="n">
-        <v>0.035</v>
+        <v>0.0343</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1472</v>
+        <v>0.1537</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1425999999999999</v>
+        <v>0.1547</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3925</v>
+        <v>0.418</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4141</v>
+        <v>0.4333</v>
       </c>
       <c r="H10" t="n">
-        <v>11.0621</v>
+        <v>10.8176</v>
       </c>
       <c r="I10" t="n">
-        <v>11.5951</v>
+        <v>10.939</v>
       </c>
     </row>
     <row r="11">
@@ -731,28 +731,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0349</v>
+        <v>0.0389</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0421</v>
+        <v>0.0345</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1417</v>
+        <v>0.1551999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1356</v>
+        <v>0.1549999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4267999999999999</v>
+        <v>0.4472</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4218999999999999</v>
+        <v>0.4571</v>
       </c>
       <c r="H11" t="n">
-        <v>11.5334</v>
+        <v>10.7612</v>
       </c>
       <c r="I11" t="n">
-        <v>11.8401</v>
+        <v>11.0062</v>
       </c>
     </row>
     <row r="12">
@@ -760,28 +760,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0336</v>
+        <v>0.0373</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0364</v>
+        <v>0.0415999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1477</v>
+        <v>0.1685</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1452</v>
+        <v>0.173</v>
       </c>
       <c r="F12" t="n">
-        <v>0.41</v>
+        <v>0.4553</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4271</v>
+        <v>0.4737</v>
       </c>
       <c r="H12" t="n">
-        <v>11.8632</v>
+        <v>10.7218</v>
       </c>
       <c r="I12" t="n">
-        <v>11.821</v>
+        <v>10.9912</v>
       </c>
     </row>
     <row r="13">
@@ -789,28 +789,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0382</v>
+        <v>0.0479999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0411</v>
+        <v>0.0445999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1543</v>
+        <v>0.1635</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1398</v>
+        <v>0.1632</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4192999999999999</v>
+        <v>0.4856999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4482</v>
+        <v>0.4782999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>11.673</v>
+        <v>10.6115</v>
       </c>
       <c r="I13" t="n">
-        <v>12.1032</v>
+        <v>10.8316</v>
       </c>
     </row>
   </sheetData>
@@ -908,28 +908,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7799043062200993</v>
+        <v>0.9067357512953316</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7955555555555556</v>
+        <v>0.9090909090909092</v>
       </c>
       <c r="D3" t="n">
-        <v>0.630896226415095</v>
+        <v>0.7214191852825226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6268656716417906</v>
+        <v>0.8537666174298361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8362014021669858</v>
+        <v>0.9475157452764167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8812154696132598</v>
+        <v>0.9029092183666312</v>
       </c>
       <c r="H3" t="n">
-        <v>1.677091295116773</v>
+        <v>1.610577127546464</v>
       </c>
       <c r="I3" t="n">
-        <v>1.705328585663617</v>
+        <v>1.592317207256734</v>
       </c>
     </row>
     <row r="4">
@@ -937,28 +937,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7581395348837209</v>
+        <v>0.7882882882882873</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7552742616033755</v>
+        <v>0.8333333333333369</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5204280155642023</v>
+        <v>0.6217440543601355</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5449101796407175</v>
+        <v>0.6864608076009497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7623474723997681</v>
+        <v>0.9283510455947891</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8491570541259983</v>
+        <v>0.8603874415497658</v>
       </c>
       <c r="H4" t="n">
-        <v>2.099391372910336</v>
+        <v>1.617053226391864</v>
       </c>
       <c r="I4" t="n">
-        <v>2.104661162710698</v>
+        <v>1.665509433962264</v>
       </c>
     </row>
     <row r="5">
@@ -966,28 +966,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5800711743772262</v>
+        <v>0.6679389312977061</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7427385892116183</v>
+        <v>0.7818930041152263</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5250245338567228</v>
+        <v>0.5539858728557003</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5079069767441851</v>
+        <v>0.5717111770524224</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7266685128773196</v>
+        <v>0.8797920727745284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7703246579017978</v>
+        <v>0.8082836523376216</v>
       </c>
       <c r="H5" t="n">
-        <v>2.308463381845812</v>
+        <v>2.286115303350438</v>
       </c>
       <c r="I5" t="n">
-        <v>2.285764988278368</v>
+        <v>2.254751038757578</v>
       </c>
     </row>
     <row r="6">
@@ -995,28 +995,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5821428571428571</v>
+        <v>0.7383966244725697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5811688311688311</v>
+        <v>0.7116104868913857</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4764024933214604</v>
+        <v>0.4858407079646009</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4682675814751278</v>
+        <v>0.5202520252025193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7260653016048704</v>
+        <v>0.7906569343065691</v>
       </c>
       <c r="G6" t="n">
-        <v>0.751373985867574</v>
+        <v>0.7096418732782366</v>
       </c>
       <c r="H6" t="n">
-        <v>2.244275026044133</v>
+        <v>2.095788444510035</v>
       </c>
       <c r="I6" t="n">
-        <v>2.271002106474393</v>
+        <v>2.058289511085844</v>
       </c>
     </row>
     <row r="7">
@@ -1024,28 +1024,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4865671641791059</v>
+        <v>0.5700325732899009</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5682539682539682</v>
+        <v>0.698529411764706</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4388843314191964</v>
+        <v>0.4448946515397075</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4364508393285364</v>
+        <v>0.5070175438596487</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7149863760217988</v>
+        <v>0.7518045530260965</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7703246579017978</v>
+        <v>0.685470995210218</v>
       </c>
       <c r="H7" t="n">
-        <v>2.193808496653367</v>
+        <v>2.125589357880556</v>
       </c>
       <c r="I7" t="n">
-        <v>2.188626262084261</v>
+        <v>2.088416612589227</v>
       </c>
     </row>
     <row r="8">
@@ -1053,28 +1053,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5326797385620915</v>
+        <v>0.5718954248365981</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5524691358024691</v>
+        <v>0.6506849315068516</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4363784665579119</v>
+        <v>0.4456168831168823</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4326465927099833</v>
+        <v>0.487763713080168</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6949152542372886</v>
+        <v>0.6938252626184983</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7361538461538464</v>
+        <v>0.7065277015907842</v>
       </c>
       <c r="H8" t="n">
-        <v>2.14581427989315</v>
+        <v>2.119403402731139</v>
       </c>
       <c r="I8" t="n">
-        <v>2.175300433762355</v>
+        <v>2.120427903401448</v>
       </c>
     </row>
     <row r="9">
@@ -1082,28 +1082,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4553072625698324</v>
+        <v>0.6505576208178402</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5682539682539682</v>
+        <v>0.6148867313915858</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3767605633802817</v>
+        <v>0.4121621621621617</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3968023255813946</v>
+        <v>0.4218978102189777</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6456692913385829</v>
+        <v>0.7118822292323868</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7259165613147914</v>
+        <v>0.6526475804408408</v>
       </c>
       <c r="H9" t="n">
-        <v>2.179843806054584</v>
+        <v>2.171603062189982</v>
       </c>
       <c r="I9" t="n">
-        <v>2.142882160306814</v>
+        <v>2.155940340724062</v>
       </c>
     </row>
     <row r="10">
@@ -1111,28 +1111,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4604519774011299</v>
+        <v>0.5485893416927869</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5114285714285713</v>
+        <v>0.5539358600583091</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3634510869565217</v>
+        <v>0.3571893298633695</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3828892005610094</v>
+        <v>0.373626373626373</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6685350318471339</v>
+        <v>0.6478468899521528</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6933107944940836</v>
+        <v>0.5945072697899836</v>
       </c>
       <c r="H10" t="n">
-        <v>2.142206271865197</v>
+        <v>2.100438174826209</v>
       </c>
       <c r="I10" t="n">
-        <v>2.110632939776285</v>
+        <v>2.1182374988573</v>
       </c>
     </row>
     <row r="11">
@@ -1140,28 +1140,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4670487106017192</v>
+        <v>0.4498714652956273</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4251781472684085</v>
+        <v>0.5507246376811593</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3775582215949189</v>
+        <v>0.3537371134020614</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4026548672566364</v>
+        <v>0.3729032258064512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6148078725398316</v>
+        <v>0.6055456171735238</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6804930078217589</v>
+        <v>0.5635528330781008</v>
       </c>
       <c r="H11" t="n">
-        <v>2.054667314061768</v>
+        <v>2.111446678809055</v>
       </c>
       <c r="I11" t="n">
-        <v>2.066958893928261</v>
+        <v>2.105304283040468</v>
       </c>
     </row>
     <row r="12">
@@ -1169,28 +1169,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4851190476190476</v>
+        <v>0.4691689008042869</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4917582417582417</v>
+        <v>0.4567307692307703</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3622207176709547</v>
+        <v>0.3258160237388718</v>
       </c>
       <c r="E12" t="n">
-        <v>0.376033057851239</v>
+        <v>0.334104046242774</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6400000000000002</v>
+        <v>0.5947726773555895</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6722079138375089</v>
+        <v>0.5438040954190413</v>
       </c>
       <c r="H12" t="n">
-        <v>1.997547036212826</v>
+        <v>2.119205730381093</v>
       </c>
       <c r="I12" t="n">
-        <v>2.070298621098046</v>
+        <v>2.108177451051751</v>
       </c>
     </row>
     <row r="13">
@@ -1198,28 +1198,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4267015706806283</v>
+        <v>0.364583333333332</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4355231143552312</v>
+        <v>0.4260089686098664</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3467271548930655</v>
+        <v>0.3357798165137608</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3905579399141623</v>
+        <v>0.354166666666666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6258049129501554</v>
+        <v>0.5575458101708872</v>
       </c>
       <c r="G13" t="n">
-        <v>0.640562248995984</v>
+        <v>0.538574116663182</v>
       </c>
       <c r="H13" t="n">
-        <v>2.030095091236185</v>
+        <v>2.14123356735617</v>
       </c>
       <c r="I13" t="n">
-        <v>2.022027232467447</v>
+        <v>2.13924074005687</v>
       </c>
     </row>
   </sheetData>
@@ -1317,28 +1317,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3899521531100497</v>
+        <v>0.4533678756476658</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3977777777777778</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3154481132075475</v>
+        <v>0.3607095926412613</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3134328358208953</v>
+        <v>0.426883308714918</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4181007010834929</v>
+        <v>0.4737578726382083</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4406077348066299</v>
+        <v>0.4514546091833156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8385456475583863</v>
+        <v>0.8052885637732318</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8526642928318084</v>
+        <v>0.7961586036283672</v>
       </c>
     </row>
     <row r="4">
@@ -1346,28 +1346,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2527131782945736</v>
+        <v>0.2627627627627624</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2517580872011252</v>
+        <v>0.277777777777779</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1734760051880674</v>
+        <v>0.2072480181200451</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1816367265469059</v>
+        <v>0.2288202692003166</v>
       </c>
       <c r="F4" t="n">
-        <v>0.254115824133256</v>
+        <v>0.3094503485315964</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2830523513753327</v>
+        <v>0.2867958138499219</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6997971243034454</v>
+        <v>0.5390177421306214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7015537209035662</v>
+        <v>0.5551698113207547</v>
       </c>
     </row>
     <row r="5">
@@ -1375,28 +1375,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1450177935943066</v>
+        <v>0.1669847328244265</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1856846473029046</v>
+        <v>0.1954732510288066</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1312561334641807</v>
+        <v>0.1384964682139251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1269767441860463</v>
+        <v>0.1429277942631056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1816671282193299</v>
+        <v>0.2199480181936321</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1925811644754495</v>
+        <v>0.2020709130844054</v>
       </c>
       <c r="H5" t="n">
-        <v>0.577115845461453</v>
+        <v>0.5715288258376094</v>
       </c>
       <c r="I5" t="n">
-        <v>0.571441247069592</v>
+        <v>0.5636877596893944</v>
       </c>
     </row>
     <row r="6">
@@ -1404,28 +1404,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1164285714285714</v>
+        <v>0.1476793248945139</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1162337662337662</v>
+        <v>0.1423220973782771</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09528049866429208</v>
+        <v>0.09716814159292017</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09365351629502557</v>
+        <v>0.1040504050405039</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1452130603209741</v>
+        <v>0.1581313868613138</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1502747971735148</v>
+        <v>0.1419283746556473</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4488550052088266</v>
+        <v>0.4191576889020071</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4542004212948785</v>
+        <v>0.4116579022171688</v>
       </c>
     </row>
     <row r="7">
@@ -1433,28 +1433,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.08109452736318432</v>
+        <v>0.09500542888165014</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0947089947089947</v>
+        <v>0.116421568627451</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07314738856986606</v>
+        <v>0.07414910858995125</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07274180655475607</v>
+        <v>0.08450292397660812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1191643960036331</v>
+        <v>0.1253007588376827</v>
       </c>
       <c r="G7" t="n">
-        <v>0.128387442983633</v>
+        <v>0.1142451658683697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3656347494422278</v>
+        <v>0.3542648929800927</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3647710436807102</v>
+        <v>0.3480694354315379</v>
       </c>
     </row>
     <row r="8">
@@ -1462,28 +1462,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.07609710550887021</v>
+        <v>0.08169934640522829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07892416225749559</v>
+        <v>0.09295499021526452</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06233978093684456</v>
+        <v>0.06365955473098318</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0618066561014262</v>
+        <v>0.06968053044002399</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09927360774818408</v>
+        <v>0.09911789465978547</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1051648351648352</v>
+        <v>0.1009325287986834</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3065448971275928</v>
+        <v>0.3027719146758771</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3107572048231936</v>
+        <v>0.3029182719144926</v>
       </c>
     </row>
     <row r="9">
@@ -1491,28 +1491,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05691340782122905</v>
+        <v>0.08131970260223002</v>
       </c>
       <c r="C9" t="n">
-        <v>0.07103174603174603</v>
+        <v>0.07686084142394822</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04709507042253522</v>
+        <v>0.05152027027027022</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04960029069767433</v>
+        <v>0.05273722627737221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08070866141732286</v>
+        <v>0.08898527865404834</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09073957016434893</v>
+        <v>0.0815809475551051</v>
       </c>
       <c r="H9" t="n">
-        <v>0.272480475756823</v>
+        <v>0.2714503827737477</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2678602700383517</v>
+        <v>0.2694925425905078</v>
       </c>
     </row>
     <row r="10">
@@ -1520,28 +1520,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05116133082234776</v>
+        <v>0.06095437129919855</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05682539682539681</v>
+        <v>0.06154842889536768</v>
       </c>
       <c r="D10" t="n">
-        <v>0.04038345410628019</v>
+        <v>0.03968770331815217</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04254324450677882</v>
+        <v>0.04151404151404144</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0742816702052371</v>
+        <v>0.07198298777246143</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07703453272156485</v>
+        <v>0.06605636330999817</v>
       </c>
       <c r="H10" t="n">
-        <v>0.238022919096133</v>
+        <v>0.2333820194251343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2345147710862538</v>
+        <v>0.2353597220952555</v>
       </c>
     </row>
     <row r="11">
@@ -1549,28 +1549,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04670487106017192</v>
+        <v>0.04498714652956273</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04251781472684085</v>
+        <v>0.05507246376811593</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03775582215949189</v>
+        <v>0.03537371134020614</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04026548672566364</v>
+        <v>0.03729032258064512</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06148078725398316</v>
+        <v>0.06055456171735239</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06804930078217589</v>
+        <v>0.05635528330781008</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2054667314061768</v>
+        <v>0.2111446678809055</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2066958893928261</v>
+        <v>0.2105304283040468</v>
       </c>
     </row>
     <row r="12">
@@ -1578,28 +1578,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0441017316017316</v>
+        <v>0.04265171825493518</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0447052947052947</v>
+        <v>0.04152097902097912</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03292915615190497</v>
+        <v>0.02961963852171562</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03418482344102172</v>
+        <v>0.03037309511297945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0581818181818182</v>
+        <v>0.05407024339596268</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06110981034886444</v>
+        <v>0.04943673594718557</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1815951851102569</v>
+        <v>0.1926550663982811</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1882089655543678</v>
+        <v>0.1916524955501591</v>
       </c>
     </row>
     <row r="13">
@@ -1607,28 +1607,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03555846422338569</v>
+        <v>0.03038194444444434</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03629359286293593</v>
+        <v>0.03550074738415553</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02889392957442212</v>
+        <v>0.02798165137614674</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03254649499284686</v>
+        <v>0.02951388888888884</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05215040941251295</v>
+        <v>0.04646215084757394</v>
       </c>
       <c r="G13" t="n">
-        <v>0.053380187416332</v>
+        <v>0.0448811763885985</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1691745909363488</v>
+        <v>0.1784361306130142</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1685022693722872</v>
+        <v>0.1782700616714059</v>
       </c>
     </row>
   </sheetData>
